--- a/data/trans_orig/P3A_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42620</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71575</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43620</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70625</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105004</t>
+          <t>105365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401319</t>
+          <t>401029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430274</t>
+          <t>429619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263060</t>
+          <t>261458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284542</t>
+          <t>284989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674571</t>
+          <t>674210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708950</t>
+          <t>710021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>30551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46335</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336283</t>
+          <t>336383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355334</t>
+          <t>355415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348924</t>
+          <t>347483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363103</t>
+          <t>363385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692464</t>
+          <t>692823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715877</t>
+          <t>716595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23220</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519169</t>
+          <t>518063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534853</t>
+          <t>534945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157216</t>
+          <t>156882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166718</t>
+          <t>166687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>682249</t>
+          <t>681433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699133</t>
+          <t>699504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>35918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1203701</t>
+          <t>1202416</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1221925</t>
+          <t>1221662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>695986</t>
+          <t>696768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708292</t>
+          <t>708925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904909</t>
+          <t>1905988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926832</t>
+          <t>1928336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339789</t>
+          <t>340371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348841</t>
+          <t>348851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>550688</t>
+          <t>550273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563678</t>
+          <t>564076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895717</t>
+          <t>895119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911438</t>
+          <t>911404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>23342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,47 +2463,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>37788</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>51775</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>37788</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>26462</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>50156</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68178</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273338</t>
+          <t>274859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289167</t>
+          <t>289251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,47 +2576,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1207942</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1193955</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1219459</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>96,97%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1207942</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1195574</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1219268</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1475752</t>
+          <t>1476475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1503768</t>
+          <t>1504864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111156</t>
+          <t>112882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>156837</t>
+          <t>156326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86911</t>
+          <t>88095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129269</t>
+          <t>129519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>208505</t>
+          <t>211550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>271183</t>
+          <t>269579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3112471</t>
+          <t>3112982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3158152</t>
+          <t>3156426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3244303</t>
+          <t>3244053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3286661</t>
+          <t>3285477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6371697</t>
+          <t>6373301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6434375</t>
+          <t>6431330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>53099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34695</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46802</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>78269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384498</t>
+          <t>384112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409868</t>
+          <t>411323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279759</t>
+          <t>279675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299228</t>
+          <t>298755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672359</t>
+          <t>673396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704863</t>
+          <t>704851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387459</t>
+          <t>388391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407149</t>
+          <t>406968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308075</t>
+          <t>309392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328000</t>
+          <t>328090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704012</t>
+          <t>704937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732320</t>
+          <t>732170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605248</t>
+          <t>603747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620425</t>
+          <t>620204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240656</t>
+          <t>240473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254759</t>
+          <t>254773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>851627</t>
+          <t>852210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872434</t>
+          <t>872719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56180</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1117210</t>
+          <t>1116442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1140103</t>
+          <t>1139800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742188</t>
+          <t>741971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759057</t>
+          <t>758960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867486</t>
+          <t>1868580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895265</t>
+          <t>1895589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62321</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475446</t>
+          <t>475896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494264</t>
+          <t>495431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727459</t>
+          <t>727668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746923</t>
+          <t>746448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1208737</t>
+          <t>1211627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1236871</t>
+          <t>1238063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>59847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94216</t>
+          <t>93602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65848</t>
+          <t>65591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101470</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252692</t>
+          <t>253717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263855</t>
+          <t>263953</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1015135</t>
+          <t>1015749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1049861</t>
+          <t>1049504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274763</t>
+          <t>1275687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1310385</t>
+          <t>1310642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112072</t>
+          <t>109493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159009</t>
+          <t>154661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136257</t>
+          <t>136514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190935</t>
+          <t>187799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258950</t>
+          <t>258680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327718</t>
+          <t>329352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3261841</t>
+          <t>3266189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3308778</t>
+          <t>3311357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3357189</t>
+          <t>3360325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3411867</t>
+          <t>3411610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6641257</t>
+          <t>6639623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6710025</t>
+          <t>6710295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59279</t>
+          <t>59204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391838</t>
+          <t>393169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413353</t>
+          <t>413789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314539</t>
+          <t>314942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334264</t>
+          <t>334310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715895</t>
+          <t>715970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743454</t>
+          <t>744150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359150</t>
+          <t>359695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372504</t>
+          <t>372539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353601</t>
+          <t>355120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368826</t>
+          <t>369170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719864</t>
+          <t>720844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>738939</t>
+          <t>739123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503090</t>
+          <t>503579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515733</t>
+          <t>515884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156346</t>
+          <t>156309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165147</t>
+          <t>165144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665509</t>
+          <t>665405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679893</t>
+          <t>679653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49782</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114430</t>
+          <t>1115000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131817</t>
+          <t>1131670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796568</t>
+          <t>796195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814671</t>
+          <t>814318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1917311</t>
+          <t>1918663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1942810</t>
+          <t>1942321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34897</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598377</t>
+          <t>598441</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612422</t>
+          <t>612235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719623</t>
+          <t>719585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733240</t>
+          <t>733155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1323099</t>
+          <t>1321887</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1343167</t>
+          <t>1342297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36465</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>67667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41862</t>
+          <t>41346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74560</t>
+          <t>74633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273437</t>
+          <t>273384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283479</t>
+          <t>283313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1014289</t>
+          <t>1014358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045560</t>
+          <t>1045273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1292775</t>
+          <t>1292702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1325473</t>
+          <t>1325989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65147</t>
+          <t>66651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100065</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87320</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133451</t>
+          <t>132792</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160304</t>
+          <t>161585</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219518</t>
+          <t>219834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3276616</t>
+          <t>3275288</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3311534</t>
+          <t>3310030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3393183</t>
+          <t>3393842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3439314</t>
+          <t>3441824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6683797</t>
+          <t>6683481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6743011</t>
+          <t>6741730</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47828</t>
+          <t>47789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55308</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>83338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457384</t>
+          <t>457423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478363</t>
+          <t>477446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404082</t>
+          <t>405058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422859</t>
+          <t>422189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869143</t>
+          <t>868647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>896677</t>
+          <t>896057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45738</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425576</t>
+          <t>423704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440211</t>
+          <t>440386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>358618</t>
+          <t>358868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370751</t>
+          <t>370758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>788588</t>
+          <t>789345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808307</t>
+          <t>808662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41289</t>
+          <t>42832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640207</t>
+          <t>639713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663967</t>
+          <t>663665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149046</t>
+          <t>148328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158729</t>
+          <t>158783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>793320</t>
+          <t>791777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824358</t>
+          <t>823349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64721</t>
+          <t>64536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52650</t>
+          <t>50631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95024</t>
+          <t>93795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970098</t>
+          <t>970283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998227</t>
+          <t>998167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941270</t>
+          <t>942236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964442</t>
+          <t>964325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1917888</t>
+          <t>1919117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960262</t>
+          <t>1962281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74451</t>
+          <t>74918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448025</t>
+          <t>448007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462851</t>
+          <t>462981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>787444</t>
+          <t>786808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809797</t>
+          <t>809354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241930</t>
+          <t>1241463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1267528</t>
+          <t>1268616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48948</t>
+          <t>49404</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73393</t>
+          <t>73695</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86159</t>
+          <t>85817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212415</t>
+          <t>219048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238431</t>
+          <t>239033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687978</t>
+          <t>687676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>712423</t>
+          <t>711967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915719</t>
+          <t>916061</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>948085</t>
+          <t>946754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114554</t>
+          <t>111672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175210</t>
+          <t>172268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155154</t>
+          <t>158670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>217074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>283406</t>
+          <t>289395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374454</t>
+          <t>375010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3200384</t>
+          <t>3203326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3261040</t>
+          <t>3263922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3359695</t>
+          <t>3359424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3421344</t>
+          <t>3417828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6577638</t>
+          <t>6577082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6668686</t>
+          <t>6662697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>69860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69554</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105365</t>
+          <t>103899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401029</t>
+          <t>403034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429619</t>
+          <t>430357</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261458</t>
+          <t>262424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284989</t>
+          <t>285166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674210</t>
+          <t>675676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710021</t>
+          <t>709018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14219</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7991</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>33544</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>23221</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>47560</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14219</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24382</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>33544</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>22204</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>45976</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336383</t>
+          <t>335728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355415</t>
+          <t>356035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>357646</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>348865</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>363874</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>705255</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>691239</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>715578</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>357646</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>347483</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>363385</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>705255</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>692823</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>716595</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518063</t>
+          <t>519369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534945</t>
+          <t>535048</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156882</t>
+          <t>158056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166687</t>
+          <t>166678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>681433</t>
+          <t>682398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699504</t>
+          <t>699751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>44431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1202416</t>
+          <t>1202712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1221662</t>
+          <t>1222044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696768</t>
+          <t>697447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708925</t>
+          <t>708185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1905988</t>
+          <t>1906667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1928336</t>
+          <t>1927786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340371</t>
+          <t>340562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348851</t>
+          <t>348932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>550273</t>
+          <t>550974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>564076</t>
+          <t>563768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895119</t>
+          <t>894977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911404</t>
+          <t>911090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23342</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274859</t>
+          <t>274719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289251</t>
+          <t>289617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1193955</t>
+          <t>1192836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1219459</t>
+          <t>1218739</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1476475</t>
+          <t>1474334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1504864</t>
+          <t>1503700</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112882</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>156326</t>
+          <t>157145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88095</t>
+          <t>87199</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129519</t>
+          <t>130077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211550</t>
+          <t>208863</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>269579</t>
+          <t>272786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3112982</t>
+          <t>3112163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3156426</t>
+          <t>3156983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3244053</t>
+          <t>3243495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3285477</t>
+          <t>3286373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6373301</t>
+          <t>6370094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6431330</t>
+          <t>6434017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53099</t>
+          <t>51810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78269</t>
+          <t>79258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384112</t>
+          <t>385401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411323</t>
+          <t>409934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279675</t>
+          <t>280284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298755</t>
+          <t>299037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673396</t>
+          <t>672407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704851</t>
+          <t>704434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388391</t>
+          <t>389429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406968</t>
+          <t>406975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309392</t>
+          <t>307768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328090</t>
+          <t>328200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704937</t>
+          <t>704250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732170</t>
+          <t>731027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25668</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603747</t>
+          <t>604648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620204</t>
+          <t>620189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240473</t>
+          <t>241406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254773</t>
+          <t>254507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852210</t>
+          <t>851271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872719</t>
+          <t>872111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>56673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1116442</t>
+          <t>1118910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1139800</t>
+          <t>1140058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741971</t>
+          <t>742335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758960</t>
+          <t>758492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1868580</t>
+          <t>1866993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895589</t>
+          <t>1893909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>34581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>32770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59431</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475896</t>
+          <t>474956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495431</t>
+          <t>495486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727668</t>
+          <t>727984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746448</t>
+          <t>747044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1211627</t>
+          <t>1210674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238063</t>
+          <t>1238288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>59869</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93602</t>
+          <t>93510</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100546</t>
+          <t>100918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>253048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263953</t>
+          <t>263813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1015749</t>
+          <t>1015841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1049504</t>
+          <t>1049482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1275687</t>
+          <t>1275315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1310642</t>
+          <t>1310979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>108965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154661</t>
+          <t>154340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136514</t>
+          <t>138353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187799</t>
+          <t>190124</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258680</t>
+          <t>259272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329352</t>
+          <t>330945</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3266189</t>
+          <t>3266510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3311357</t>
+          <t>3311885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3360325</t>
+          <t>3358000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3411610</t>
+          <t>3409771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6639623</t>
+          <t>6638030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6710295</t>
+          <t>6709703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59204</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393169</t>
+          <t>393110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413789</t>
+          <t>414056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>314942</t>
+          <t>314189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334310</t>
+          <t>334614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715970</t>
+          <t>716669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744150</t>
+          <t>744288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359695</t>
+          <t>359675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372539</t>
+          <t>372515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355120</t>
+          <t>354551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369170</t>
+          <t>368333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720844</t>
+          <t>720603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>739123</t>
+          <t>739587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503579</t>
+          <t>504213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515884</t>
+          <t>515850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156309</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165144</t>
+          <t>165153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665405</t>
+          <t>665176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679653</t>
+          <t>679052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>32144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25674</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1115000</t>
+          <t>1113081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131670</t>
+          <t>1131195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796195</t>
+          <t>795702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814318</t>
+          <t>813910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918663</t>
+          <t>1917701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1942321</t>
+          <t>1942257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598441</t>
+          <t>598047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>612235</t>
+          <t>612276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719585</t>
+          <t>719702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733155</t>
+          <t>732805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1321887</t>
+          <t>1322331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1342297</t>
+          <t>1342384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67667</t>
+          <t>67506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41346</t>
+          <t>40869</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74633</t>
+          <t>73921</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273384</t>
+          <t>273120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283313</t>
+          <t>283326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1014358</t>
+          <t>1014519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1045273</t>
+          <t>1045934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1292702</t>
+          <t>1293414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1325989</t>
+          <t>1326466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66651</t>
+          <t>66011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101393</t>
+          <t>104279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84810</t>
+          <t>85406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132792</t>
+          <t>133531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161585</t>
+          <t>163029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219834</t>
+          <t>221919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3275288</t>
+          <t>3272402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3310030</t>
+          <t>3310670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3393842</t>
+          <t>3393103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3441824</t>
+          <t>3441228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6683481</t>
+          <t>6681396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6741730</t>
+          <t>6740286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47789</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41715</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>61629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>90926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>468762</t>
+          <t>511519</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457423</t>
+          <t>498662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477446</t>
+          <t>521166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>414522</t>
+          <t>452221</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405058</t>
+          <t>441538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422189</t>
+          <t>460825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>883284</t>
+          <t>963740</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>868647</t>
+          <t>947426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>896057</t>
+          <t>976723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44981</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>433696</t>
+          <t>463364</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423704</t>
+          <t>453750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440386</t>
+          <t>470672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>365649</t>
+          <t>402286</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>358868</t>
+          <t>393984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370758</t>
+          <t>408534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>799345</t>
+          <t>865649</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>789345</t>
+          <t>854442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808662</t>
+          <t>876604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>45446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>652755</t>
+          <t>452803</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639713</t>
+          <t>442466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663665</t>
+          <t>459302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>154453</t>
+          <t>172782</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148328</t>
+          <t>165890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158783</t>
+          <t>177768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>807208</t>
+          <t>625584</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791777</t>
+          <t>613094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823349</t>
+          <t>633345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>52913</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>40407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64536</t>
+          <t>71089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>21191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>36520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>81131</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>66842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93795</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>985961</t>
+          <t>1078930</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970283</t>
+          <t>1060754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998167</t>
+          <t>1091436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>952190</t>
+          <t>832993</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942236</t>
+          <t>824691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964325</t>
+          <t>840020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1938150</t>
+          <t>1911923</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919117</t>
+          <t>1893204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962281</t>
+          <t>1926212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>66109</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74918</t>
+          <t>79450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>457088</t>
+          <t>548763</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448007</t>
+          <t>539454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462981</t>
+          <t>554947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>797382</t>
+          <t>783942</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>786808</t>
+          <t>773651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809354</t>
+          <t>792579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1254470</t>
+          <t>1332705</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241463</t>
+          <t>1319364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1268616</t>
+          <t>1344251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49404</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73695</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67963</t>
+          <t>71915</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55124</t>
+          <t>58378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85817</t>
+          <t>89113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232534</t>
+          <t>229563</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219048</t>
+          <t>215113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239033</t>
+          <t>236193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>701381</t>
+          <t>780031</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687676</t>
+          <t>765859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711967</t>
+          <t>792014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>933915</t>
+          <t>1009594</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>916061</t>
+          <t>992396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946754</t>
+          <t>1023131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>144798</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>134453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172268</t>
+          <t>182303</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>190921</t>
+          <t>209892</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158670</t>
+          <t>187436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>232055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>335720</t>
+          <t>366945</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289395</t>
+          <t>335311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>375010</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3230796</t>
+          <t>3284940</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3203326</t>
+          <t>3259690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3263922</t>
+          <t>3307540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3385577</t>
+          <t>3424256</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3359424</t>
+          <t>3402093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3417828</t>
+          <t>3446712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6616372</t>
+          <t>6709195</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6577082</t>
+          <t>6673958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6662697</t>
+          <t>6740829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
